--- a/one down/普物實驗/2 RC 電路對直流與交流訊號的反應/E24146107_王翊權_預報2_表格.xlsx
+++ b/one down/普物實驗/2 RC 電路對直流與交流訊號的反應/E24146107_王翊權_預報2_表格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\school\one down\普物實驗\2 RC 電路對直流與交流訊號的反應\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A2171C-3D33-4B5F-B455-19A8338B3313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AAF235E-FF2C-4FA4-861E-1C682A10C080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="18648" windowHeight="11784" activeTab="1" xr2:uid="{E94D7E06-B847-4966-AA45-058955BF689A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{E94D7E06-B847-4966-AA45-058955BF689A}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表4" sheetId="4" r:id="rId1"/>
@@ -37,31 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
-  <si>
-    <t>電容</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>電阻</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>hz</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>半衰期</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>充電時間</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>放電時間</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
   <si>
     <t>臨界頻率</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -148,15 +124,43 @@
     <t>f (Hz)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>頻率 (Hz)</t>
+  </si>
+  <si>
+    <t>半衰期 (μs)</t>
+  </si>
+  <si>
+    <t>充電時間 (μs)</t>
+  </si>
+  <si>
+    <t>放電時間 (μs)</t>
+  </si>
+  <si>
+    <t>輸入頻率 f (Hz)</t>
+  </si>
+  <si>
+    <t>角頻率 ω (rad/s)</t>
+  </si>
+  <si>
+    <t>電容電壓 V_c (V)</t>
+  </si>
+  <si>
+    <t>電阻電壓 V_R (V)</t>
+  </si>
+  <si>
+    <t>\tau</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
+    <numFmt numFmtId="176" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -223,6 +227,12 @@
       <charset val="161"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -232,10 +242,45 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -246,7 +291,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -256,11 +301,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1358,16 +1412,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>483577</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>141654</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>54707</xdr:rowOff>
+      <xdr:rowOff>209386</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>210038</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>130907</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>478692</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>65779</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1712,67 +1766,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA78F8E-4615-46E5-A0AA-9A5F60793D7E}">
-  <dimension ref="A1:L32"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <dimension ref="A1:AE27"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:31" ht="46.5">
+      <c r="A1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="S1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="X1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE1" s="7"/>
+    </row>
+    <row r="2" spans="1:31">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="L2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3">
+      <c r="U2" s="5">
         <v>100</v>
       </c>
-      <c r="B3">
-        <v>98</v>
-      </c>
-      <c r="C3">
-        <v>400</v>
-      </c>
-      <c r="D3">
-        <v>480</v>
-      </c>
-      <c r="F3">
+      <c r="V2" s="5">
+        <v>114</v>
+      </c>
+      <c r="W2" s="5">
+        <v>600</v>
+      </c>
+      <c r="X2" s="5">
+        <v>108</v>
+      </c>
+      <c r="AA2" s="5">
         <v>100</v>
       </c>
-      <c r="G3">
-        <v>114</v>
-      </c>
+      <c r="AB2" s="5">
+        <v>628</v>
+      </c>
+      <c r="AC2" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="AD2" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31">
       <c r="J3" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K3">
         <v>1185</v>
@@ -1781,441 +1852,726 @@
         <f>2*PI()*K3</f>
         <v>7445.5745890078097</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="B4">
+      <c r="U3" s="5">
+        <v>100</v>
+      </c>
+      <c r="V3" s="5">
+        <v>116</v>
+      </c>
+      <c r="W3" s="5">
+        <v>600</v>
+      </c>
+      <c r="X3" s="5">
+        <v>112</v>
+      </c>
+      <c r="AA3" s="5">
+        <v>200</v>
+      </c>
+      <c r="AB3" s="5">
+        <v>1257</v>
+      </c>
+      <c r="AC3" s="5">
+        <v>0.49</v>
+      </c>
+      <c r="AD3" s="5">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31">
+      <c r="U4" s="5">
+        <v>100</v>
+      </c>
+      <c r="V4" s="5">
+        <v>111</v>
+      </c>
+      <c r="W4" s="5">
+        <v>600</v>
+      </c>
+      <c r="X4" s="5">
+        <v>100</v>
+      </c>
+      <c r="AA4" s="5">
+        <v>400</v>
+      </c>
+      <c r="AB4" s="5">
+        <v>2513</v>
+      </c>
+      <c r="AC4" s="5">
+        <v>0.48</v>
+      </c>
+      <c r="AD4" s="5">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31">
+      <c r="U5" s="5">
+        <v>100</v>
+      </c>
+      <c r="V5" s="5">
+        <v>117</v>
+      </c>
+      <c r="W5" s="5">
+        <v>600</v>
+      </c>
+      <c r="X5" s="5">
+        <v>104</v>
+      </c>
+      <c r="AA5" s="5">
+        <v>800</v>
+      </c>
+      <c r="AB5" s="5">
+        <v>5027</v>
+      </c>
+      <c r="AC5" s="5">
+        <v>0.43</v>
+      </c>
+      <c r="AD5" s="5">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31">
+      <c r="U6" s="5">
+        <v>100</v>
+      </c>
+      <c r="V6" s="5">
+        <v>110</v>
+      </c>
+      <c r="W6" s="5">
+        <v>600</v>
+      </c>
+      <c r="X6" s="5">
+        <v>104</v>
+      </c>
+      <c r="AA6" s="5">
+        <v>1000</v>
+      </c>
+      <c r="AB6" s="5">
+        <v>6283</v>
+      </c>
+      <c r="AC6" s="5">
+        <v>0.41</v>
+      </c>
+      <c r="AD6" s="5">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31">
+      <c r="U7" s="5">
+        <v>200</v>
+      </c>
+      <c r="V7" s="5">
+        <v>90</v>
+      </c>
+      <c r="W7" s="5">
+        <v>800</v>
+      </c>
+      <c r="X7" s="5">
+        <v>90</v>
+      </c>
+      <c r="AA7" s="5">
+        <v>1500</v>
+      </c>
+      <c r="AB7" s="5">
+        <v>9425</v>
+      </c>
+      <c r="AC7" s="5">
+        <v>0.37</v>
+      </c>
+      <c r="AD7" s="5">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31">
+      <c r="U8" s="5">
+        <v>200</v>
+      </c>
+      <c r="V8" s="5">
+        <v>90</v>
+      </c>
+      <c r="W8" s="5">
+        <v>800</v>
+      </c>
+      <c r="X8" s="5">
+        <v>88</v>
+      </c>
+      <c r="AA8" s="5">
+        <v>1592</v>
+      </c>
+      <c r="AB8" s="5">
+        <v>10003</v>
+      </c>
+      <c r="AC8" s="5">
+        <v>0.36</v>
+      </c>
+      <c r="AD8" s="5">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31">
+      <c r="D9" s="2"/>
+      <c r="U9" s="5">
+        <v>200</v>
+      </c>
+      <c r="V9" s="5">
+        <v>90</v>
+      </c>
+      <c r="W9" s="5">
+        <v>800</v>
+      </c>
+      <c r="X9" s="5">
+        <v>92</v>
+      </c>
+      <c r="AA9" s="5">
+        <v>2000</v>
+      </c>
+      <c r="AB9" s="5">
+        <v>12566</v>
+      </c>
+      <c r="AC9" s="5">
+        <v>0.32</v>
+      </c>
+      <c r="AD9" s="5">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31">
+      <c r="U10" s="5">
+        <v>200</v>
+      </c>
+      <c r="V10" s="5">
+        <v>90</v>
+      </c>
+      <c r="W10" s="5">
+        <v>800</v>
+      </c>
+      <c r="X10" s="5">
+        <v>92</v>
+      </c>
+      <c r="AA10" s="5">
+        <v>4000</v>
+      </c>
+      <c r="AB10" s="5">
+        <v>25133</v>
+      </c>
+      <c r="AC10" s="5">
+        <v>0.19</v>
+      </c>
+      <c r="AD10" s="5">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31">
+      <c r="U11" s="5">
+        <v>200</v>
+      </c>
+      <c r="V11" s="5">
+        <v>90</v>
+      </c>
+      <c r="W11" s="5">
+        <v>800</v>
+      </c>
+      <c r="X11" s="5">
+        <v>88</v>
+      </c>
+      <c r="AA11" s="5">
+        <v>6000</v>
+      </c>
+      <c r="AB11" s="5">
+        <v>37699</v>
+      </c>
+      <c r="AC11" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="AD11" s="5">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" ht="31">
+      <c r="F12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="U12" s="5">
+        <v>400</v>
+      </c>
+      <c r="V12" s="5">
+        <v>100</v>
+      </c>
+      <c r="W12" s="5">
+        <v>1000</v>
+      </c>
+      <c r="X12" s="5">
+        <v>100</v>
+      </c>
+      <c r="AA12" s="5">
+        <v>10000</v>
+      </c>
+      <c r="AB12" s="5">
+        <v>62832</v>
+      </c>
+      <c r="AC12" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="AD12" s="5">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31">
+      <c r="F13" s="5">
+        <v>100</v>
+      </c>
+      <c r="G13" s="5">
+        <v>98</v>
+      </c>
+      <c r="H13" s="5">
+        <v>400</v>
+      </c>
+      <c r="I13" s="5">
+        <v>480</v>
+      </c>
+      <c r="J13" s="5">
+        <v>600</v>
+      </c>
+      <c r="K13" s="5">
+        <v>88</v>
+      </c>
+      <c r="L13" s="5">
+        <v>258</v>
+      </c>
+      <c r="M13" s="5">
+        <v>294</v>
+      </c>
+      <c r="U13" s="5">
+        <v>400</v>
+      </c>
+      <c r="V13" s="5">
+        <v>96</v>
+      </c>
+      <c r="W13" s="5">
+        <v>1000</v>
+      </c>
+      <c r="X13" s="5">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31">
+      <c r="F14" s="5">
+        <v>100</v>
+      </c>
+      <c r="G14" s="5">
         <v>102</v>
       </c>
-      <c r="C4">
+      <c r="H14" s="5">
         <v>430</v>
       </c>
-      <c r="D4">
+      <c r="I14" s="5">
         <v>420</v>
       </c>
-      <c r="G4">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="B5">
+      <c r="J14" s="5">
+        <v>600</v>
+      </c>
+      <c r="K14" s="5">
+        <v>88</v>
+      </c>
+      <c r="L14" s="5">
+        <v>264</v>
+      </c>
+      <c r="M14" s="5">
+        <v>294</v>
+      </c>
+      <c r="U14" s="5">
+        <v>400</v>
+      </c>
+      <c r="V14" s="5">
+        <v>100</v>
+      </c>
+      <c r="W14" s="5">
+        <v>1000</v>
+      </c>
+      <c r="X14" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31">
+      <c r="F15" s="5">
+        <v>100</v>
+      </c>
+      <c r="G15" s="5">
         <v>124</v>
       </c>
-      <c r="C5">
+      <c r="H15" s="5">
         <v>360</v>
       </c>
-      <c r="D5">
+      <c r="I15" s="5">
         <v>390</v>
       </c>
-      <c r="G5">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="B6">
+      <c r="J15" s="5">
+        <v>600</v>
+      </c>
+      <c r="K15" s="5">
+        <v>88</v>
+      </c>
+      <c r="L15" s="5">
+        <v>280</v>
+      </c>
+      <c r="M15" s="5">
+        <v>294</v>
+      </c>
+      <c r="U15" s="5">
+        <v>400</v>
+      </c>
+      <c r="V15" s="5">
+        <v>104</v>
+      </c>
+      <c r="W15" s="5">
+        <v>1000</v>
+      </c>
+      <c r="X15" s="5">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31">
+      <c r="F16" s="5">
+        <v>100</v>
+      </c>
+      <c r="G16" s="5">
         <v>90</v>
       </c>
-      <c r="C6">
+      <c r="H16" s="5">
         <v>370</v>
       </c>
-      <c r="D6">
+      <c r="I16" s="5">
         <v>310</v>
       </c>
-      <c r="G6">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="B7">
+      <c r="J16" s="5">
+        <v>600</v>
+      </c>
+      <c r="K16" s="5">
+        <v>88</v>
+      </c>
+      <c r="L16" s="5">
+        <v>280</v>
+      </c>
+      <c r="M16" s="5">
+        <v>294</v>
+      </c>
+      <c r="U16" s="5">
+        <v>400</v>
+      </c>
+      <c r="V16" s="5">
+        <v>100</v>
+      </c>
+      <c r="W16" s="5">
+        <v>1000</v>
+      </c>
+      <c r="X16" s="5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="6:13">
+      <c r="F17" s="5">
+        <v>100</v>
+      </c>
+      <c r="G17" s="5">
         <v>96</v>
       </c>
-      <c r="C7">
+      <c r="H17" s="5">
         <v>470</v>
       </c>
-      <c r="D7">
+      <c r="I17" s="5">
         <v>400</v>
       </c>
-      <c r="G7">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8">
+      <c r="J17" s="5">
+        <v>600</v>
+      </c>
+      <c r="K17" s="5">
+        <v>88</v>
+      </c>
+      <c r="L17" s="5">
+        <v>280</v>
+      </c>
+      <c r="M17" s="5">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="18" spans="6:13">
+      <c r="F18" s="5">
         <v>200</v>
       </c>
-      <c r="B8">
+      <c r="G18" s="5">
         <v>102</v>
       </c>
-      <c r="C8">
+      <c r="H18" s="5">
         <v>334</v>
       </c>
-      <c r="D8">
+      <c r="I18" s="5">
         <v>360</v>
       </c>
-      <c r="F8">
+      <c r="J18" s="5">
+        <v>800</v>
+      </c>
+      <c r="K18" s="5">
+        <v>90</v>
+      </c>
+      <c r="L18" s="5">
+        <v>290</v>
+      </c>
+      <c r="M18" s="5">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="19" spans="6:13">
+      <c r="F19" s="5">
         <v>200</v>
       </c>
-      <c r="G8">
+      <c r="G19" s="5">
+        <v>127</v>
+      </c>
+      <c r="H19" s="5">
+        <v>278</v>
+      </c>
+      <c r="I19" s="5">
+        <v>366</v>
+      </c>
+      <c r="J19" s="5">
+        <v>800</v>
+      </c>
+      <c r="K19" s="5">
+        <v>88</v>
+      </c>
+      <c r="L19" s="5">
+        <v>290</v>
+      </c>
+      <c r="M19" s="5">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="20" spans="6:13">
+      <c r="F20" s="5">
+        <v>200</v>
+      </c>
+      <c r="G20" s="5">
+        <v>92</v>
+      </c>
+      <c r="H20" s="5">
+        <v>278</v>
+      </c>
+      <c r="I20" s="5">
+        <v>320</v>
+      </c>
+      <c r="J20" s="5">
+        <v>800</v>
+      </c>
+      <c r="K20" s="5">
+        <v>88</v>
+      </c>
+      <c r="L20" s="5">
+        <v>280</v>
+      </c>
+      <c r="M20" s="5">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="21" spans="6:13">
+      <c r="F21" s="5">
+        <v>200</v>
+      </c>
+      <c r="G21" s="5">
+        <v>91</v>
+      </c>
+      <c r="H21" s="5">
+        <v>280</v>
+      </c>
+      <c r="I21" s="5">
+        <v>330</v>
+      </c>
+      <c r="J21" s="5">
+        <v>800</v>
+      </c>
+      <c r="K21" s="5">
+        <v>88</v>
+      </c>
+      <c r="L21" s="5">
+        <v>278</v>
+      </c>
+      <c r="M21" s="5">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="22" spans="6:13">
+      <c r="F22" s="5">
+        <v>200</v>
+      </c>
+      <c r="G22" s="5">
+        <v>91</v>
+      </c>
+      <c r="H22" s="5">
+        <v>280</v>
+      </c>
+      <c r="I22" s="5">
+        <v>328</v>
+      </c>
+      <c r="J22" s="5">
+        <v>800</v>
+      </c>
+      <c r="K22" s="5">
+        <v>88</v>
+      </c>
+      <c r="L22" s="5">
+        <v>278</v>
+      </c>
+      <c r="M22" s="5">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="23" spans="6:13">
+      <c r="F23" s="5">
+        <v>400</v>
+      </c>
+      <c r="G23" s="5">
+        <v>91</v>
+      </c>
+      <c r="H23" s="5">
+        <v>274</v>
+      </c>
+      <c r="I23" s="5">
+        <v>300</v>
+      </c>
+      <c r="J23" s="5">
+        <v>1000</v>
+      </c>
+      <c r="K23" s="5">
+        <v>88</v>
+      </c>
+      <c r="L23" s="5">
+        <v>296</v>
+      </c>
+      <c r="M23" s="5">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="24" spans="6:13">
+      <c r="F24" s="5">
+        <v>400</v>
+      </c>
+      <c r="G24" s="5">
+        <v>91</v>
+      </c>
+      <c r="H24" s="5">
+        <v>274</v>
+      </c>
+      <c r="I24" s="5">
+        <v>280</v>
+      </c>
+      <c r="J24" s="5">
+        <v>1000</v>
+      </c>
+      <c r="K24" s="5">
+        <v>88</v>
+      </c>
+      <c r="L24" s="5">
+        <v>296</v>
+      </c>
+      <c r="M24" s="5">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="25" spans="6:13">
+      <c r="F25" s="5">
+        <v>400</v>
+      </c>
+      <c r="G25" s="5">
+        <v>91</v>
+      </c>
+      <c r="H25" s="5">
+        <v>274</v>
+      </c>
+      <c r="I25" s="5">
+        <v>298</v>
+      </c>
+      <c r="J25" s="5">
+        <v>1000</v>
+      </c>
+      <c r="K25" s="5">
+        <v>89</v>
+      </c>
+      <c r="L25" s="5">
+        <v>296</v>
+      </c>
+      <c r="M25" s="5">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="26" spans="6:13">
+      <c r="F26" s="5">
+        <v>400</v>
+      </c>
+      <c r="G26" s="5">
+        <v>91</v>
+      </c>
+      <c r="H26" s="5">
+        <v>274</v>
+      </c>
+      <c r="I26" s="5">
+        <v>300</v>
+      </c>
+      <c r="J26" s="5">
+        <v>1000</v>
+      </c>
+      <c r="K26" s="5">
         <v>90</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="B9">
-        <v>127</v>
-      </c>
-      <c r="C9">
-        <v>278</v>
-      </c>
-      <c r="D9" s="2">
-        <v>366</v>
-      </c>
-      <c r="G9">
+      <c r="L26" s="5">
+        <v>290</v>
+      </c>
+      <c r="M26" s="5">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="27" spans="6:13">
+      <c r="F27" s="5">
+        <v>400</v>
+      </c>
+      <c r="G27" s="5">
         <v>90</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="B10">
-        <v>92</v>
-      </c>
-      <c r="C10">
-        <v>278</v>
-      </c>
-      <c r="D10">
-        <v>320</v>
-      </c>
-      <c r="G10">
+      <c r="H27" s="5">
+        <v>274</v>
+      </c>
+      <c r="I27" s="5">
+        <v>280</v>
+      </c>
+      <c r="J27" s="5">
+        <v>1000</v>
+      </c>
+      <c r="K27" s="5">
         <v>90</v>
       </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="B11">
-        <v>91</v>
-      </c>
-      <c r="C11">
-        <v>280</v>
-      </c>
-      <c r="D11">
-        <v>330</v>
-      </c>
-      <c r="G11">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="B12">
-        <v>91</v>
-      </c>
-      <c r="C12">
-        <v>280</v>
-      </c>
-      <c r="D12">
-        <v>328</v>
-      </c>
-      <c r="G12">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13">
-        <v>400</v>
-      </c>
-      <c r="B13">
-        <v>91</v>
-      </c>
-      <c r="C13">
-        <v>274</v>
-      </c>
-      <c r="D13">
-        <v>300</v>
-      </c>
-      <c r="F13">
-        <v>400</v>
-      </c>
-      <c r="G13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="B14">
-        <v>91</v>
-      </c>
-      <c r="C14">
-        <v>274</v>
-      </c>
-      <c r="D14">
-        <v>280</v>
-      </c>
-      <c r="G14">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="B15">
-        <v>91</v>
-      </c>
-      <c r="C15">
-        <v>274</v>
-      </c>
-      <c r="D15">
-        <v>298</v>
-      </c>
-      <c r="G15">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="B16">
-        <v>91</v>
-      </c>
-      <c r="C16">
-        <v>274</v>
-      </c>
-      <c r="D16">
-        <v>300</v>
-      </c>
-      <c r="G16">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="B17">
-        <v>90</v>
-      </c>
-      <c r="C17">
-        <v>274</v>
-      </c>
-      <c r="D17">
-        <v>280</v>
-      </c>
-      <c r="G17">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>600</v>
-      </c>
-      <c r="B18">
-        <v>88</v>
-      </c>
-      <c r="C18">
-        <v>258</v>
-      </c>
-      <c r="D18">
-        <v>294</v>
-      </c>
-      <c r="F18">
-        <v>600</v>
-      </c>
-      <c r="G18">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="B19">
-        <v>88</v>
-      </c>
-      <c r="C19">
-        <v>264</v>
-      </c>
-      <c r="D19">
-        <v>294</v>
-      </c>
-      <c r="G19">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="B20">
-        <v>88</v>
-      </c>
-      <c r="C20">
-        <v>280</v>
-      </c>
-      <c r="D20">
-        <v>294</v>
-      </c>
-      <c r="G20">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="B21">
-        <v>88</v>
-      </c>
-      <c r="C21">
-        <v>280</v>
-      </c>
-      <c r="D21">
-        <v>294</v>
-      </c>
-      <c r="G21">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="B22">
-        <v>88</v>
-      </c>
-      <c r="C22">
-        <v>280</v>
-      </c>
-      <c r="D22">
-        <v>294</v>
-      </c>
-      <c r="G22">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>800</v>
-      </c>
-      <c r="B23">
-        <v>90</v>
-      </c>
-      <c r="C23">
-        <v>290</v>
-      </c>
-      <c r="D23">
+      <c r="L27" s="5">
         <v>292</v>
       </c>
-      <c r="F23">
-        <v>800</v>
-      </c>
-      <c r="G23">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="B24">
-        <v>88</v>
-      </c>
-      <c r="C24">
-        <v>290</v>
-      </c>
-      <c r="D24">
-        <v>292</v>
-      </c>
-      <c r="G24">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="B25">
-        <v>88</v>
-      </c>
-      <c r="C25">
-        <v>280</v>
-      </c>
-      <c r="D25">
-        <v>292</v>
-      </c>
-      <c r="G25">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="B26">
-        <v>88</v>
-      </c>
-      <c r="C26">
-        <v>278</v>
-      </c>
-      <c r="D26">
-        <v>292</v>
-      </c>
-      <c r="G26">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="B27">
-        <v>88</v>
-      </c>
-      <c r="C27">
-        <v>278</v>
-      </c>
-      <c r="D27">
-        <v>292</v>
-      </c>
-      <c r="G27">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>1000</v>
-      </c>
-      <c r="B28">
-        <v>88</v>
-      </c>
-      <c r="C28">
-        <v>296</v>
-      </c>
-      <c r="D28">
-        <v>294</v>
-      </c>
-      <c r="F28">
-        <v>1000</v>
-      </c>
-      <c r="G28">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="B29">
-        <v>88</v>
-      </c>
-      <c r="C29">
-        <v>296</v>
-      </c>
-      <c r="D29">
+      <c r="M27" s="5">
         <v>288</v>
-      </c>
-      <c r="G29">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="B30">
-        <v>89</v>
-      </c>
-      <c r="C30">
-        <v>296</v>
-      </c>
-      <c r="D30">
-        <v>288</v>
-      </c>
-      <c r="G30">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="B31">
-        <v>90</v>
-      </c>
-      <c r="C31">
-        <v>290</v>
-      </c>
-      <c r="D31">
-        <v>288</v>
-      </c>
-      <c r="G31">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="B32">
-        <v>90</v>
-      </c>
-      <c r="C32">
-        <v>292</v>
-      </c>
-      <c r="D32">
-        <v>288</v>
-      </c>
-      <c r="G32">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2227,20 +2583,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E24E7CD2-F1E0-4403-AC33-DDC61830C6D4}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:4">
